--- a/inst/notebooks/makers_details.xlsx
+++ b/inst/notebooks/makers_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/24b25e554f22146a/Masters Class notes/AIMS Rwanda/Thesis Phase/Publication Phase/Refactoring MalReBay/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\SwissTPH-Ubuntu-24.04\home\golumo\GitRepos\MalReBay\inst\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{D403CC85-76BC-4478-A233-D1D2E70AF80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26417E7E-DC63-4EC6-BCA3-4C1AF67F6512}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33DDC83-9ECF-47B4-A1E6-FF6326F77DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7B200665-48F8-48D7-B17C-7D3B5710279D}"/>
+    <workbookView xWindow="0" yWindow="980" windowWidth="19380" windowHeight="9830" xr2:uid="{7B200665-48F8-48D7-B17C-7D3B5710279D}"/>
   </bookViews>
   <sheets>
     <sheet name="markers_info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="45">
   <si>
     <t>marker_id</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>TRAP3</t>
+  </si>
+  <si>
+    <t>cpmp1</t>
   </si>
 </sst>
 </file>
@@ -539,15 +542,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E4F913-EFD9-4818-926C-D0A818E637D6}">
-  <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>313</v>
       </c>
@@ -575,7 +578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>383</v>
       </c>
@@ -589,7 +592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -603,7 +606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -617,7 +620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -631,7 +634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -645,7 +648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2490</v>
       </c>
@@ -659,7 +662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -673,7 +676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -687,7 +690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -701,7 +704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -715,7 +718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -729,7 +732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -743,7 +746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -757,7 +760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -771,7 +774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -785,7 +788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -799,7 +802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -813,7 +816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -827,7 +830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -841,7 +844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -855,7 +858,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -869,7 +872,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -883,7 +886,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -897,7 +900,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -911,7 +914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -925,7 +928,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -939,7 +942,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -953,7 +956,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -967,7 +970,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -981,7 +984,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -995,7 +998,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1023,7 +1026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1068,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1079,7 +1082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1090,6 +1093,20 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
         <v>39</v>
       </c>
     </row>

--- a/inst/notebooks/makers_details.xlsx
+++ b/inst/notebooks/makers_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\SwissTPH-Ubuntu-24.04\home\golumo\GitRepos\MalReBay\inst\notebooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\MalReBay-Package\MalReBay\inst\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33DDC83-9ECF-47B4-A1E6-FF6326F77DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F742158D-9736-4AE3-A469-7175A3109C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="980" windowWidth="19380" windowHeight="9830" xr2:uid="{7B200665-48F8-48D7-B17C-7D3B5710279D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7B200665-48F8-48D7-B17C-7D3B5710279D}"/>
   </bookViews>
   <sheets>
     <sheet name="markers_info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="62">
   <si>
     <t>marker_id</t>
   </si>
@@ -171,6 +171,57 @@
   </si>
   <si>
     <t>cpmp1</t>
+  </si>
+  <si>
+    <t>celtos</t>
+  </si>
+  <si>
+    <t>surfin1.1</t>
+  </si>
+  <si>
+    <t>ama1-D2</t>
+  </si>
+  <si>
+    <t>ama1-D2.1</t>
+  </si>
+  <si>
+    <t>TRAP2</t>
+  </si>
+  <si>
+    <t>ama1-D3.3</t>
+  </si>
+  <si>
+    <t>csp1</t>
+  </si>
+  <si>
+    <t>msp7.2</t>
+  </si>
+  <si>
+    <t>ama1-D2.3</t>
+  </si>
+  <si>
+    <t>ama1-D3.2</t>
+  </si>
+  <si>
+    <t>cpp3</t>
+  </si>
+  <si>
+    <t>msp7.3</t>
+  </si>
+  <si>
+    <t>cpmp3</t>
+  </si>
+  <si>
+    <t>TRAP4_</t>
+  </si>
+  <si>
+    <t>ama1-D3.4</t>
+  </si>
+  <si>
+    <t>cpmp2</t>
+  </si>
+  <si>
+    <t>cpp1</t>
   </si>
 </sst>
 </file>
@@ -542,15 +593,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E4F913-EFD9-4818-926C-D0A818E637D6}">
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D64"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,7 +617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>313</v>
       </c>
@@ -578,7 +631,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>383</v>
       </c>
@@ -592,7 +645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -606,7 +659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -620,7 +673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -634,7 +687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -648,7 +701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2490</v>
       </c>
@@ -662,7 +715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -676,7 +729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -690,7 +743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -704,7 +757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -718,7 +771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -732,7 +785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -746,7 +799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -760,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -774,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -788,7 +841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -802,7 +855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -816,7 +869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -830,7 +883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -844,7 +897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -858,7 +911,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -872,7 +925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -886,7 +939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -900,7 +953,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -914,7 +967,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -928,7 +981,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -942,7 +995,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -956,7 +1009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -970,7 +1023,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -984,7 +1037,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -998,7 +1051,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1065,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1026,7 +1079,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1040,7 +1093,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1054,7 +1107,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -1068,7 +1121,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1082,7 +1135,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1096,7 +1149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1107,6 +1160,342 @@
         <v>38</v>
       </c>
       <c r="D40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
+        <v>38</v>
+      </c>
+      <c r="D59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" t="s">
+        <v>38</v>
+      </c>
+      <c r="D64" t="s">
         <v>39</v>
       </c>
     </row>
